--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T13:45:36+00:00</t>
+    <t>2026-05-11T13:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
